--- a/thesis/slides/進捗報告_20260817_図表データ.xlsx
+++ b/thesis/slides/進捗報告_20260817_図表データ.xlsx
@@ -23,6 +23,13 @@
     <sheet name="風力×裁定指標" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="duration曲線" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="量と価格の関係" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="価格水準θ" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="π(K)水準感応度" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="均衡面" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="フロンティア" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="空間分散" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="BTM回避率" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="燃料危機期除外" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2315,6 +2322,1128 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>月次 θ_m</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'価格水準θ'!H4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0079C2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'価格水準θ'!$G$5:$G$55</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'価格水準θ'!$H$5:$H$55</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>θ</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>π_実現可能(K) シナリオ別</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'π(K)水準感応度'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0079C2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'π(K)水準感応度'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'π(K)水準感応度'!$B$5:$B$12</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'π(K)水準感応度'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="D95B20"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'π(K)水準感応度'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'π(K)水準感応度'!$C$5:$C$12</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'π(K)水準感応度'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="176871"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'π(K)水準感応度'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'π(K)水準感応度'!$D$5:$D$12</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'π(K)水準感応度'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7B3F9E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'π(K)水準感応度'!$A$5:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'π(K)水準感応度'!$E$5:$E$12</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>円/kW-年</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>π(K; K_wind) 泊なし</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'均衡面'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0079C2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'均衡面'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'均衡面'!$B$5:$B$11</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'均衡面'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="D95B20"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'均衡面'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'均衡面'!$C$5:$C$11</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'均衡面'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="176871"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'均衡面'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'均衡面'!$D$5:$D$11</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'均衡面'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7B3F9E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'均衡面'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'均衡面'!$E$5:$E$11</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'均衡面'!F4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="9DC3E6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'均衡面'!$A$5:$A$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'均衡面'!$F$5:$F$11</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>円/kW-年</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>π(K; K_wind) 泊あり</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'均衡面'!B15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0079C2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'均衡面'!$A$16:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'均衡面'!$B$16:$B$22</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'均衡面'!C15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="D95B20"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'均衡面'!$A$16:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'均衡面'!$C$16:$C$22</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'均衡面'!D15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="176871"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'均衡面'!$A$16:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'均衡面'!$D$16:$D$22</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'均衡面'!E15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="7B3F9E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'均衡面'!$A$16:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'均衡面'!$E$16:$E$22</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'均衡面'!F15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="9DC3E6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'均衡面'!$A$16:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'均衡面'!$F$16:$F$22</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>円/kW-年</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>PF価値 vs λ</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'空間分散'!K3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0079C2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'空間分散'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'空間分散'!$K$4:$K$8</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>円/kW-年</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>風力→TB4h 係数 vs λ</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'空間分散'!M3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0079C2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'空間分散'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'空間分散'!$M$4:$M$8</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'空間分散'!O3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="D95B20"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'空間分散'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'空間分散'!$O$4:$O$8</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'空間分散'!Q3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="176871"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'空間分散'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'空間分散'!$Q$4:$Q$8</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>円/kWh per GWh/日</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
@@ -3549,6 +4678,158 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -4054,7 +5335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4266,6 +5547,90 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>追加: 発電量五分位×価格水準・TB4hスプレッド（風力vs太陽光・季節別）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>価格水準θ</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>追加(9/29): 供給曲線v2の年度別・月次の価格水準係数θ（表8.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>π(K)水準感応度</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>追加(9/29): θ=1／FY2026上期／FY2022／泊 の π(K) と損益分岐θ*（表8.5・図8.4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>均衡面</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>追加(9/29): 風力0.5〜3×の均衡面（表8.6・図8.3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>フロンティア</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>追加(9/29): θ*格子・K*格子・P_cap(K)（表9.2・9.3・8.7、図9.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>空間分散</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>追加(9/29): 集中立地の反実仮想（表6.4・図6.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BTM回避率</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>追加(9/29): 回避可能率 一様／集中（表9.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>燃料危機期除外</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>追加(9/29): 6.5.4 の頑健性（表6.8）</t>
         </is>
       </c>
     </row>
@@ -7845,6 +9210,1815 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>供給曲線v2の価格水準係数 θ（FY2023-25 の時間加重平均=1）: 年度別と月次</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>年度別 θ</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>月次 θ_m（価格水準指数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>θ_FY</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>平均価格(北海道)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>平均システムプライス</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>年月</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>θ_m</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>平均価格(北海道)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>平均システムプライス</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.715</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I5" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17.76</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="I7" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="I8" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2.191</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.52</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I10" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.02</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.864</v>
+      </c>
+      <c r="I11" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="I12" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="I13" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.04</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1.398</v>
+      </c>
+      <c r="I14" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="J14" t="n">
+        <v>19.56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1.165</v>
+      </c>
+      <c r="I15" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="J15" t="n">
+        <v>15.06</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="I20" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10.13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="I21" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="J21" t="n">
+        <v>11.68</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1.092</v>
+      </c>
+      <c r="I22" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13.39</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I23" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="J23" t="n">
+        <v>11.24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="I24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="I25" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="J26" t="n">
+        <v>10.12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9.359999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="I28" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10.66</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="I29" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="J29" t="n">
+        <v>9.44</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="I30" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="J30" t="n">
+        <v>9.619999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1.173</v>
+      </c>
+      <c r="I31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>10.92</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="I32" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="I33" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="J33" t="n">
+        <v>14.48</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="I34" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="J34" t="n">
+        <v>13.96</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="I35" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="J35" t="n">
+        <v>12.68</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="I36" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="J36" t="n">
+        <v>12.42</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="I37" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="J37" t="n">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1.177</v>
+      </c>
+      <c r="I38" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="J38" t="n">
+        <v>12.43</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I39" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="J39" t="n">
+        <v>13.94</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="I40" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="J40" t="n">
+        <v>11.31</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="J41" t="n">
+        <v>9.82</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>8.92</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="J43" t="n">
+        <v>10.87</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="I44" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="J44" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="I45" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="J45" t="n">
+        <v>11.98</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="I46" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="J46" t="n">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="I47" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="J47" t="n">
+        <v>11.67</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="I48" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="J48" t="n">
+        <v>10.55</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1.039</v>
+      </c>
+      <c r="I49" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J49" t="n">
+        <v>10.58</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I50" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="J50" t="n">
+        <v>11.27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="I51" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="J51" t="n">
+        <v>10.45</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="I52" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="J52" t="n">
+        <v>12.12</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="I53" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="J53" t="n">
+        <v>14.77</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>1.668</v>
+      </c>
+      <c r="I54" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="J54" t="n">
+        <v>14.06</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1.525</v>
+      </c>
+      <c r="I55" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="J55" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>π(K) の価格水準感応度（供給曲線v2、円/kW-年、括弧なし=モデル値、_裾補正=×1.25）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>π_実現可能(K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>K(万kW)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>FY2022水準（θ=1.72）</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>FY2026上期水準（θ=1.57）</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>FY2026上期水準＋泊3号再稼働</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>現状（FY2023-25水準 θ=1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9733</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8738</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9277</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4943</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8175</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7315</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7881</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5353</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4737</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5480</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2995</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2584</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3550</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-416</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-532</v>
+      </c>
+      <c r="D9" t="n">
+        <v>345</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-974</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-1477</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1501</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1020</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1592</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>200</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-1735</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1736</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1407</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1742</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>300</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-1751</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1751</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-1483</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1751</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>π_実現可能_裾補正(K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>K(万kW)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>FY2022水準（θ=1.72）</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>FY2026上期水準（θ=1.57）</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>FY2026上期水準＋泊3号再稼働</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>現状（FY2023-25水準 θ=1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>12572</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11331</v>
+      </c>
+      <c r="D17" t="n">
+        <v>12003</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6598</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" t="n">
+        <v>10629</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9556</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10261</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5465</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7108</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6341</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7267</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3413</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>50</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4168</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3655</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4860</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-86</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-231</v>
+      </c>
+      <c r="D21" t="n">
+        <v>863</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-781</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>150</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-1409</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1439</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-839</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1552</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>200</v>
+      </c>
+      <c r="B23" t="n">
+        <v>-1730</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1732</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1321</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1739</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>300</v>
+      </c>
+      <c r="B24" t="n">
+        <v>-1751</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1751</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-1417</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1751</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>損益分岐の θ*（K=0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>必要水準(円/kW-年)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>θ*</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>θ*_裾補正</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>対FY2026上期(倍)</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>対FY2026上期_裾補正(倍)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>標準（容量1.25万・c_req3.45万）</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>楽観（容量1.25万・c_req3.2万）</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>19500</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>保守（容量0.83万・c_req3.7万）</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>28700</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>均衡面 π(K; K_wind, 泊)（供給曲線v2 θ=1、円/kW-年）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>泊なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>K(万kW)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>風力×0.5</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>風力×1.0</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>風力×1.5</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>風力×2.0</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>風力×3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4815</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4943</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5116</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5373</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6055</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3895</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4035</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4210</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4480</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5184</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2196</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2389</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2610</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2947</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B8" t="n">
+        <v>823</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1317</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1628</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-1123</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-974</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-742</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-446</v>
+      </c>
+      <c r="F9" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-1644</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1592</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1507</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1364</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-798</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>200</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-1746</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1742</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1717</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1658</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1249</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>泊あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>K(万kW)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>風力×0.5</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>風力×1.0</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>風力×1.5</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>風力×2.0</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>風力×3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5091</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5287</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5467</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5667</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5582</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4214</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4396</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4623</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4816</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4903</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>25</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2711</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2863</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3117</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3404</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3658</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>50</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1464</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1843</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2192</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-579</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-414</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-188</v>
+      </c>
+      <c r="E20" t="n">
+        <v>129</v>
+      </c>
+      <c r="F20" t="n">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>150</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-1393</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1285</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-1065</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-746</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-69</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>200</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-1629</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1532</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1355</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-1058</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-387</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7930,6 +11104,3437 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F88"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>break-even フロンティア: θ*(資本費, 実効容量収入)・K* 格子・P_cap(K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>θ*（WACC 5%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>資本費(万円/kWh)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>0.83万（発動指令）</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>0（容量収入なし）</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>1.25万（現行・安定電源）</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>1.75万（2030年度向けNet CONE 20,911円）</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>2.5万（上限近傍3万円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>θ*（WACC 6%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>資本費(万円/kWh)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>0.83万（発動指令）</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0（容量収入なし）</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>1.25万（現行・安定電源）</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>1.75万（2030年度向けNet CONE 20,911円）</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>2.5万（上限近傍3万円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>θ*（WACC 8%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>資本費(万円/kWh)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>0.83万（発動指令）</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>0（容量収入なし）</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>1.25万（現行・安定電源）</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>1.75万（2030年度向けNet CONE 20,911円）</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>2.5万（上限近傍3万円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="C28" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>K* 格子（万kW、WACC6%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>θ</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>資本費(万円/kWh)</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>κP_cap</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>K*_容量定数(万kW)</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>K*_北海道按分(万kW)</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>K*_全国連系(万kW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>θ=1（FY2023-25）</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>θ=1（FY2023-25）</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>21</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>θ=1（FY2023-25）</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>200</v>
+      </c>
+      <c r="E34" t="n">
+        <v>15</v>
+      </c>
+      <c r="F34" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>θ=1（FY2023-25）</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>θ=1（FY2023-25）</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>θ=1（FY2023-25）</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>49</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>θ=1（FY2023-25）</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>θ=1（FY2023-25）</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>θ=1（FY2023-25）</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>θ=1.57（FY2026上期）</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>θ=1.57（FY2026上期）</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>48</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>θ=1.57（FY2026上期）</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>200</v>
+      </c>
+      <c r="E43" t="n">
+        <v>20</v>
+      </c>
+      <c r="F43" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>θ=1.57（FY2026上期）</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>θ=1.57（FY2026上期）</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>θ=1.57（FY2026上期）</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>74</v>
+      </c>
+      <c r="E46" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>θ=1.57（FY2026上期）</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>θ=1.57（FY2026上期）</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>θ=1.57（FY2026上期）</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>θ=1.72（FY2022）</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>θ=1.72（FY2022）</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>53</v>
+      </c>
+      <c r="E51" t="n">
+        <v>8</v>
+      </c>
+      <c r="F51" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>θ=1.72（FY2022）</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>200</v>
+      </c>
+      <c r="E52" t="n">
+        <v>21</v>
+      </c>
+      <c r="F52" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>θ=1.72（FY2022）</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>θ=1.72（FY2022）</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>θ=1.72（FY2022）</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>78</v>
+      </c>
+      <c r="E55" t="n">
+        <v>11</v>
+      </c>
+      <c r="F55" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>θ=1.72（FY2022）</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>θ=1.72（FY2022）</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>θ=1.72（FY2022）</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>θ=2.5</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>31</v>
+      </c>
+      <c r="E59" t="n">
+        <v>7</v>
+      </c>
+      <c r="F59" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>θ=2.5</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>74</v>
+      </c>
+      <c r="E60" t="n">
+        <v>15</v>
+      </c>
+      <c r="F60" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>θ=2.5</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>200</v>
+      </c>
+      <c r="E61" t="n">
+        <v>31</v>
+      </c>
+      <c r="F61" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>θ=2.5</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>θ=2.5</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>24</v>
+      </c>
+      <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>θ=2.5</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>4</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>91</v>
+      </c>
+      <c r="E64" t="n">
+        <v>18</v>
+      </c>
+      <c r="F64" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>θ=2.5</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>θ=2.5</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>θ=2.5</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>16</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>θ=3.0</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>42</v>
+      </c>
+      <c r="E68" t="n">
+        <v>12</v>
+      </c>
+      <c r="F68" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>θ=3.0</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>81</v>
+      </c>
+      <c r="E69" t="n">
+        <v>19</v>
+      </c>
+      <c r="F69" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>θ=3.0</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>200</v>
+      </c>
+      <c r="E70" t="n">
+        <v>43</v>
+      </c>
+      <c r="F70" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>θ=3.0</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>15</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>θ=3.0</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>37</v>
+      </c>
+      <c r="E72" t="n">
+        <v>11</v>
+      </c>
+      <c r="F72" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>θ=3.0</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>95</v>
+      </c>
+      <c r="E73" t="n">
+        <v>21</v>
+      </c>
+      <c r="F73" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>θ=3.0</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1.25万</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>θ=3.0</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1.75万</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>θ=3.0</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2.5万</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>24</v>
+      </c>
+      <c r="E76" t="n">
+        <v>7</v>
+      </c>
+      <c r="F76" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>容量市場価格の K 依存 P_cap(K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>K(万kW)</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>P_cap 北海道ブロック按分(円/kW)</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>κP_cap 北海道ブロック按分(円/kW-年)</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>P_cap 全国連系(円/kW)</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>κP_cap 全国連系(円/kW-年)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>0</v>
+      </c>
+      <c r="B80" t="n">
+        <v>14972</v>
+      </c>
+      <c r="C80" t="n">
+        <v>12517</v>
+      </c>
+      <c r="D80" t="n">
+        <v>14972</v>
+      </c>
+      <c r="E80" t="n">
+        <v>12517</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>5</v>
+      </c>
+      <c r="B81" t="n">
+        <v>9791</v>
+      </c>
+      <c r="C81" t="n">
+        <v>8185</v>
+      </c>
+      <c r="D81" t="n">
+        <v>14789</v>
+      </c>
+      <c r="E81" t="n">
+        <v>12364</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>10</v>
+      </c>
+      <c r="B82" t="n">
+        <v>7522</v>
+      </c>
+      <c r="C82" t="n">
+        <v>6288</v>
+      </c>
+      <c r="D82" t="n">
+        <v>14607</v>
+      </c>
+      <c r="E82" t="n">
+        <v>12211</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>25</v>
+      </c>
+      <c r="B83" t="n">
+        <v>714</v>
+      </c>
+      <c r="C83" t="n">
+        <v>597</v>
+      </c>
+      <c r="D83" t="n">
+        <v>14059</v>
+      </c>
+      <c r="E83" t="n">
+        <v>11753</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>50</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>13145</v>
+      </c>
+      <c r="E84" t="n">
+        <v>10989</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>100</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>11318</v>
+      </c>
+      <c r="E85" t="n">
+        <v>9462</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>150</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>9839</v>
+      </c>
+      <c r="E86" t="n">
+        <v>8225</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>200</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>9098</v>
+      </c>
+      <c r="E87" t="n">
+        <v>7606</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>300</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>7616</v>
+      </c>
+      <c r="E88" t="n">
+        <v>6367</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>空間分散シミュレーション: 日内帯域の振幅倍率 λ と価格指標・風力→TB4h係数</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>λ</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>日内シェア(&lt;24h,%)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>&lt;6h(%)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>6-24h(%)</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>1-7d(%)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>&gt;7d(%)</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>床時間(h/年)</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>TB4h中央値</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>p05</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>p95</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>PF価値(円/kW-年)</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>日次エネルギー相関</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>β_wind→TB4h 夏</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>p 夏</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>β_wind→TB4h 冬</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>p 冬</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>β_wind→TB4h 春秋</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>p 春秋</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>115</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8266</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.08400000000000001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>116</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8344</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.08599999999999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>117</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8456</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>126</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8673</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>126</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8846</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>併設蓄電池の容量制約下での抑制回避可能率（北海道風力、2025/4〜2026/6）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>併設仕様</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>E(kWh/kW)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>P(kW/kW)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>回避可能率_一様(%)</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>回避可能率_集中20%/77%(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0.64kWh/kW・4h</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>65.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0.64kWh/kW・2h</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D5" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>67.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1.28kWh/kW・4h</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>84.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2.0kWh/kW・4h</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>注: 集中=容量シェア20%のサイトに抑制の77%（Maji et al. 2025 の ERCOT 分布を援用）。フリート集約 SoC シミュレーション（analysis/30）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>日次回帰: 主分析（FY2016-25）と燃料危機期（FY2021-22）除外の係数比較</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>被説明変数</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>係数</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>推定値_主分析</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>p値_主分析</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>推定値_除外</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>p値_除外</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>solar_夏</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.4598</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.3188</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>wind_夏</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.2819</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.2193</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>solar_冬</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.7557</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.6403</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0024</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>wind_冬</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.3538</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.3024</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>solar_春秋</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.347</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.1929</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>wind_春秋</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3578</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.2954</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>solar_夏</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9361</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>wind_夏</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1285</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.0779</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0444</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>solar_冬</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.3071</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.225</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>wind_冬</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1308</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1402</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>solar_春秋</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0935</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>wind_春秋</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.0276</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6712</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>solar_夏</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.0961</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.4354</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9542</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>wind_夏</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.3485</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.1852</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0868</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>solar_冬</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.8034</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.5616</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.089</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>wind_冬</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.3639</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.3887</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>solar_春秋</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>hokkaido</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>wind_春秋</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.06900000000000001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.2281</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.0176</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7418</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>solar_夏</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.0639</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.0383</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0008</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>wind_夏</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1917</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>solar_冬</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.0614</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.0555</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0267</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>wind_冬</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.2726</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.1703</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.3245</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1879</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>solar_春秋</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.0467</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>水準: 日平均価格</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>wind_春秋</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.8516</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>solar_夏</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.0017</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.7924</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>wind_夏</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.09950000000000001</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.1022</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.2585</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>solar_冬</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>wind_冬</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.1357</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2022</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.2345</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>solar_春秋</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>変動性: 日内SD</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>wind_春秋</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.0789</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0243</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>solar_夏</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9449</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>wind_夏</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.2479</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.2683</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.2572</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>solar_冬</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.1229</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.0878</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0205</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>wind_冬</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.3509</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-0.6181</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0648</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>solar_春秋</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.0862</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>kyushu</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>変動性: TB4hスプレッド</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>wind_春秋</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0608</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/thesis/slides/進捗報告_20260817_図表データ.xlsx
+++ b/thesis/slides/進捗報告_20260817_図表データ.xlsx
@@ -1,35 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="目次" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="分断方向転換" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="capture率" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="帯域分解" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="泊DC_2x2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="文献構成" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="風力スイープ" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="年間裁定粗利" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="帯域分解時系列" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="併設BTM検討" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="帯域分解比較" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="価格カーブ形状" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="風力価格カーブ" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="風力×裁定指標" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="duration曲線" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="量と価格の関係" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="価格水準θ" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="π(K)水準感応度" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="均衡面" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="フロンティア" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="空間分散" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="BTM回避率" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="燃料危機期除外" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目次" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分断方向転換" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="capture率" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="帯域分解" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="泊DC_2x2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文献構成" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="風力スイープ" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年間裁定粗利" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="帯域分解時系列" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="併設BTM検討" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="帯域分解比較" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="価格カーブ形状" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="風力価格カーブ" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="風力×裁定指標" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="duration曲線" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="量と価格の関係" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="価格水準θ" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="π(K)水準感応度" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="均衡面" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="フロンティア" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="空間分散" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BTM回避率" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="燃料危機期除外" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -189,13 +189,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -219,7 +219,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -243,7 +243,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -285,8 +285,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -312,13 +312,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -342,7 +342,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -366,7 +366,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -418,13 +418,13 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -447,7 +447,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="5DB6E7"/>
               </a:solidFill>
@@ -457,7 +457,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -483,7 +483,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -493,7 +493,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -519,7 +519,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="176871"/>
               </a:solidFill>
@@ -529,7 +529,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -555,7 +555,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -565,7 +565,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -620,13 +620,13 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -649,7 +649,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="5DB6E7"/>
               </a:solidFill>
@@ -659,7 +659,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -685,7 +685,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -695,7 +695,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -721,7 +721,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="176871"/>
               </a:solidFill>
@@ -731,7 +731,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -757,7 +757,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -767,7 +767,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -822,18 +822,18 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>需要期・夏（7-8月）</a:t>
+              <a:t>需要期・夏（7-9月）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -851,7 +851,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -861,7 +861,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -887,7 +887,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -897,7 +897,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -927,8 +927,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -955,8 +955,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -982,13 +982,13 @@
 </file>
 
 <file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1011,7 +1011,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -1021,7 +1021,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1047,7 +1047,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -1057,7 +1057,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1087,8 +1087,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1115,8 +1115,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1142,13 +1142,13 @@
 </file>
 
 <file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1171,7 +1171,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -1181,7 +1181,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1207,7 +1207,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -1217,7 +1217,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1247,8 +1247,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1275,8 +1275,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1302,18 +1302,18 @@
 </file>
 
 <file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>需要期・夏（7-8月）</a:t>
+              <a:t>需要期・夏（7-9月）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1331,7 +1331,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -1341,7 +1341,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1366,7 +1366,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -1376,7 +1376,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1430,13 +1430,13 @@
 </file>
 
 <file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1459,7 +1459,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -1469,7 +1469,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1494,7 +1494,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -1504,7 +1504,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1558,13 +1558,13 @@
 </file>
 
 <file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1587,7 +1587,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -1597,7 +1597,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1622,7 +1622,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -1632,7 +1632,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1686,13 +1686,13 @@
 </file>
 
 <file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1716,7 +1716,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1740,7 +1740,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1764,7 +1764,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1816,13 +1816,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1846,7 +1846,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1888,8 +1888,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1912,13 +1912,13 @@
 </file>
 
 <file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1942,7 +1942,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1991,13 +1991,13 @@
 </file>
 
 <file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2020,7 +2020,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -2030,7 +2030,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2056,7 +2056,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="176871"/>
               </a:solidFill>
@@ -2066,7 +2066,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2092,7 +2092,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -2102,7 +2102,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2157,13 +2157,13 @@
 </file>
 
 <file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2186,7 +2186,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -2196,7 +2196,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2222,7 +2222,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="176871"/>
               </a:solidFill>
@@ -2232,7 +2232,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2258,7 +2258,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -2268,7 +2268,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2323,13 +2323,13 @@
 </file>
 
 <file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2352,7 +2352,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -2362,7 +2362,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2405,8 +2405,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2432,13 +2432,13 @@
 </file>
 
 <file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2461,7 +2461,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -2471,7 +2471,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2497,7 +2497,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -2507,7 +2507,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2533,7 +2533,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="176871"/>
               </a:solidFill>
@@ -2543,7 +2543,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2569,7 +2569,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="7B3F9E"/>
               </a:solidFill>
@@ -2579,7 +2579,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2622,8 +2622,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2649,13 +2649,13 @@
 </file>
 
 <file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2678,7 +2678,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -2688,7 +2688,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2714,7 +2714,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -2724,7 +2724,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2750,7 +2750,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="176871"/>
               </a:solidFill>
@@ -2760,7 +2760,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2786,7 +2786,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="7B3F9E"/>
               </a:solidFill>
@@ -2796,7 +2796,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2822,7 +2822,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="9DC3E6"/>
               </a:solidFill>
@@ -2832,7 +2832,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2875,8 +2875,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2902,13 +2902,13 @@
 </file>
 
 <file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -2931,7 +2931,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -2941,7 +2941,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2967,7 +2967,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -2977,7 +2977,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3003,7 +3003,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="176871"/>
               </a:solidFill>
@@ -3013,7 +3013,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3039,7 +3039,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="7B3F9E"/>
               </a:solidFill>
@@ -3049,7 +3049,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3075,7 +3075,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="9DC3E6"/>
               </a:solidFill>
@@ -3085,7 +3085,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3128,8 +3128,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -3155,13 +3155,13 @@
 </file>
 
 <file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -3184,7 +3184,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -3194,7 +3194,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3237,8 +3237,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -3264,13 +3264,13 @@
 </file>
 
 <file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -3293,7 +3293,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -3303,7 +3303,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3329,7 +3329,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -3339,7 +3339,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3365,7 +3365,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="176871"/>
               </a:solidFill>
@@ -3375,7 +3375,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3418,8 +3418,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -3445,13 +3445,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -3475,7 +3475,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -3517,8 +3517,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -3541,13 +3541,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -3571,7 +3571,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -3613,8 +3613,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -3637,13 +3637,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -3667,7 +3667,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -3709,8 +3709,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -3733,13 +3733,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -3757,7 +3757,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -3767,7 +3767,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3788,7 +3788,7 @@
           <idx val="1"/>
           <order val="1"/>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -3798,7 +3798,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3853,13 +3853,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -3882,7 +3882,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="A6BE0B"/>
               </a:solidFill>
@@ -3892,7 +3892,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3918,7 +3918,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -3928,7 +3928,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3954,7 +3954,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="5DB6E7"/>
               </a:solidFill>
@@ -3964,7 +3964,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -3990,7 +3990,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -4000,7 +4000,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4055,13 +4055,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -4084,7 +4084,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="5DB6E7"/>
               </a:solidFill>
@@ -4094,7 +4094,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4120,7 +4120,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="0079C2"/>
               </a:solidFill>
@@ -4130,7 +4130,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4156,7 +4156,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="176871"/>
               </a:solidFill>
@@ -4166,7 +4166,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4192,7 +4192,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="D95B20"/>
               </a:solidFill>
@@ -4202,7 +4202,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4257,13 +4257,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -4287,7 +4287,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -4336,7 +4336,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -4351,9 +4351,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4363,7 +4363,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -4378,9 +4378,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4400,9 +4400,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4422,9 +4422,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4434,7 +4434,7 @@
 </file>
 
 <file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -4449,9 +4449,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4471,9 +4471,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4493,9 +4493,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4505,7 +4505,7 @@
 </file>
 
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -4520,9 +4520,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4542,9 +4542,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4564,9 +4564,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4576,7 +4576,7 @@
 </file>
 
 <file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -4591,9 +4591,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4603,7 +4603,7 @@
 </file>
 
 <file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -4618,9 +4618,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4630,7 +4630,7 @@
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -4645,9 +4645,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4667,9 +4667,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4679,7 +4679,7 @@
 </file>
 
 <file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>12</col>
@@ -4694,9 +4694,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4706,7 +4706,7 @@
 </file>
 
 <file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -4721,9 +4721,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4733,7 +4733,7 @@
 </file>
 
 <file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -4748,9 +4748,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4770,9 +4770,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4782,7 +4782,7 @@
 </file>
 
 <file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -4797,9 +4797,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4819,9 +4819,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4831,7 +4831,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -4846,9 +4846,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4858,7 +4858,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -4873,9 +4873,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4885,7 +4885,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -4900,9 +4900,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4912,7 +4912,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -4927,9 +4927,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4939,7 +4939,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -4954,9 +4954,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4966,7 +4966,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -4981,9 +4981,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4993,7 +4993,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -5008,9 +5008,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -5020,7 +5020,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
@@ -5035,9 +5035,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -6553,7 +6553,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>需要期・夏（7-8月）</t>
+          <t>需要期・夏（7-9月）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -6619,10 +6619,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>11.76</v>
+        <v>11.8</v>
       </c>
       <c r="C5" t="n">
-        <v>11.78</v>
+        <v>12.07</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6631,7 +6631,7 @@
         <v>11.65</v>
       </c>
       <c r="F5" t="n">
-        <v>11.26</v>
+        <v>11.25</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>10.69</v>
+        <v>10.92</v>
       </c>
       <c r="C6" t="n">
-        <v>10.96</v>
+        <v>11.36</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -6660,7 +6660,7 @@
         <v>11.48</v>
       </c>
       <c r="F6" t="n">
-        <v>11.19</v>
+        <v>11.15</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -6677,10 +6677,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>10.77</v>
+        <v>11.05</v>
       </c>
       <c r="C7" t="n">
-        <v>11.15</v>
+        <v>11.46</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -6689,7 +6689,7 @@
         <v>11.63</v>
       </c>
       <c r="F7" t="n">
-        <v>11.32</v>
+        <v>11.28</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -6706,10 +6706,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="n">
-        <v>11.21</v>
+        <v>11.43</v>
       </c>
       <c r="C8" t="n">
-        <v>11.42</v>
+        <v>11.72</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -6718,7 +6718,7 @@
         <v>11.83</v>
       </c>
       <c r="F8" t="n">
-        <v>11.3</v>
+        <v>11.29</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -6735,10 +6735,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>11.44</v>
+        <v>11.67</v>
       </c>
       <c r="C9" t="n">
-        <v>11.61</v>
+        <v>11.92</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -6747,7 +6747,7 @@
         <v>12.01</v>
       </c>
       <c r="F9" t="n">
-        <v>11.35</v>
+        <v>11.34</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -6764,10 +6764,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>10.52</v>
+        <v>11.02</v>
       </c>
       <c r="C10" t="n">
-        <v>11.15</v>
+        <v>11.73</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -6776,7 +6776,7 @@
         <v>12.15</v>
       </c>
       <c r="F10" t="n">
-        <v>11.48</v>
+        <v>11.49</v>
       </c>
       <c r="G10" t="n">
         <v>5</v>
@@ -6793,10 +6793,10 @@
         <v>6</v>
       </c>
       <c r="B11" t="n">
-        <v>9.779999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="C11" t="n">
-        <v>10.57</v>
+        <v>11.15</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -6805,7 +6805,7 @@
         <v>13.45</v>
       </c>
       <c r="F11" t="n">
-        <v>12.55</v>
+        <v>12.51</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
@@ -6822,10 +6822,10 @@
         <v>7</v>
       </c>
       <c r="B12" t="n">
-        <v>8.59</v>
+        <v>8.58</v>
       </c>
       <c r="C12" t="n">
-        <v>10.43</v>
+        <v>10.87</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
@@ -6834,7 +6834,7 @@
         <v>13.38</v>
       </c>
       <c r="F12" t="n">
-        <v>12.78</v>
+        <v>12.69</v>
       </c>
       <c r="G12" t="n">
         <v>7</v>
@@ -6851,10 +6851,10 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>9.18</v>
+        <v>8.66</v>
       </c>
       <c r="C13" t="n">
-        <v>11.14</v>
+        <v>11.61</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
@@ -6863,7 +6863,7 @@
         <v>12.59</v>
       </c>
       <c r="F13" t="n">
-        <v>12.75</v>
+        <v>12.7</v>
       </c>
       <c r="G13" t="n">
         <v>8</v>
@@ -6880,10 +6880,10 @@
         <v>9</v>
       </c>
       <c r="B14" t="n">
-        <v>8.58</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>11.41</v>
+        <v>12.14</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
@@ -6892,7 +6892,7 @@
         <v>11.26</v>
       </c>
       <c r="F14" t="n">
-        <v>12.23</v>
+        <v>12.22</v>
       </c>
       <c r="G14" t="n">
         <v>9</v>
@@ -6909,10 +6909,10 @@
         <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>7.56</v>
+        <v>7.19</v>
       </c>
       <c r="C15" t="n">
-        <v>10.35</v>
+        <v>11.22</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -6921,7 +6921,7 @@
         <v>9.6</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>10.99</v>
       </c>
       <c r="G15" t="n">
         <v>10</v>
@@ -6938,10 +6938,10 @@
         <v>11</v>
       </c>
       <c r="B16" t="n">
-        <v>7.68</v>
+        <v>7.24</v>
       </c>
       <c r="C16" t="n">
-        <v>10.66</v>
+        <v>11.55</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -6967,10 +6967,10 @@
         <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>7.21</v>
+        <v>6.86</v>
       </c>
       <c r="C17" t="n">
-        <v>9.67</v>
+        <v>10.46</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -6996,10 +6996,10 @@
         <v>13</v>
       </c>
       <c r="B18" t="n">
-        <v>9.789999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>12.14</v>
+        <v>12.78</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -7008,7 +7008,7 @@
         <v>8.98</v>
       </c>
       <c r="F18" t="n">
-        <v>11.17</v>
+        <v>11.18</v>
       </c>
       <c r="G18" t="n">
         <v>13</v>
@@ -7025,10 +7025,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="n">
-        <v>11.26</v>
+        <v>10.7</v>
       </c>
       <c r="C19" t="n">
-        <v>13.52</v>
+        <v>14.16</v>
       </c>
       <c r="D19" t="n">
         <v>14</v>
@@ -7037,7 +7037,7 @@
         <v>10.18</v>
       </c>
       <c r="F19" t="n">
-        <v>11.31</v>
+        <v>11.32</v>
       </c>
       <c r="G19" t="n">
         <v>14</v>
@@ -7054,10 +7054,10 @@
         <v>15</v>
       </c>
       <c r="B20" t="n">
-        <v>13.79</v>
+        <v>13.52</v>
       </c>
       <c r="C20" t="n">
-        <v>14.82</v>
+        <v>15.91</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -7066,7 +7066,7 @@
         <v>11.97</v>
       </c>
       <c r="F20" t="n">
-        <v>12.69</v>
+        <v>12.61</v>
       </c>
       <c r="G20" t="n">
         <v>15</v>
@@ -7083,10 +7083,10 @@
         <v>16</v>
       </c>
       <c r="B21" t="n">
-        <v>16.76</v>
+        <v>17.38</v>
       </c>
       <c r="C21" t="n">
-        <v>17.48</v>
+        <v>19.23</v>
       </c>
       <c r="D21" t="n">
         <v>16</v>
@@ -7095,7 +7095,7 @@
         <v>13.59</v>
       </c>
       <c r="F21" t="n">
-        <v>13.57</v>
+        <v>13.42</v>
       </c>
       <c r="G21" t="n">
         <v>16</v>
@@ -7112,10 +7112,10 @@
         <v>17</v>
       </c>
       <c r="B22" t="n">
-        <v>18.11</v>
+        <v>19.02</v>
       </c>
       <c r="C22" t="n">
-        <v>18.35</v>
+        <v>19.96</v>
       </c>
       <c r="D22" t="n">
         <v>17</v>
@@ -7124,7 +7124,7 @@
         <v>14.86</v>
       </c>
       <c r="F22" t="n">
-        <v>14.09</v>
+        <v>13.97</v>
       </c>
       <c r="G22" t="n">
         <v>17</v>
@@ -7141,10 +7141,10 @@
         <v>18</v>
       </c>
       <c r="B23" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="C23" t="n">
         <v>19.74</v>
-      </c>
-      <c r="C23" t="n">
-        <v>19</v>
       </c>
       <c r="D23" t="n">
         <v>18</v>
@@ -7153,7 +7153,7 @@
         <v>14.8</v>
       </c>
       <c r="F23" t="n">
-        <v>13.88</v>
+        <v>13.72</v>
       </c>
       <c r="G23" t="n">
         <v>18</v>
@@ -7170,10 +7170,10 @@
         <v>19</v>
       </c>
       <c r="B24" t="n">
-        <v>18.6</v>
+        <v>18.18</v>
       </c>
       <c r="C24" t="n">
-        <v>18.55</v>
+        <v>18.36</v>
       </c>
       <c r="D24" t="n">
         <v>19</v>
@@ -7182,7 +7182,7 @@
         <v>14.12</v>
       </c>
       <c r="F24" t="n">
-        <v>13.31</v>
+        <v>13.16</v>
       </c>
       <c r="G24" t="n">
         <v>19</v>
@@ -7199,10 +7199,10 @@
         <v>20</v>
       </c>
       <c r="B25" t="n">
-        <v>17.32</v>
+        <v>16.94</v>
       </c>
       <c r="C25" t="n">
-        <v>16.51</v>
+        <v>16.61</v>
       </c>
       <c r="D25" t="n">
         <v>20</v>
@@ -7211,7 +7211,7 @@
         <v>13.64</v>
       </c>
       <c r="F25" t="n">
-        <v>13.03</v>
+        <v>12.94</v>
       </c>
       <c r="G25" t="n">
         <v>20</v>
@@ -7228,10 +7228,10 @@
         <v>21</v>
       </c>
       <c r="B26" t="n">
-        <v>14.7</v>
+        <v>14.53</v>
       </c>
       <c r="C26" t="n">
-        <v>15.05</v>
+        <v>15.12</v>
       </c>
       <c r="D26" t="n">
         <v>21</v>
@@ -7240,7 +7240,7 @@
         <v>13.01</v>
       </c>
       <c r="F26" t="n">
-        <v>12.28</v>
+        <v>12.22</v>
       </c>
       <c r="G26" t="n">
         <v>21</v>
@@ -7257,10 +7257,10 @@
         <v>22</v>
       </c>
       <c r="B27" t="n">
-        <v>13.57</v>
+        <v>13.48</v>
       </c>
       <c r="C27" t="n">
-        <v>13.33</v>
+        <v>13.59</v>
       </c>
       <c r="D27" t="n">
         <v>22</v>
@@ -7269,7 +7269,7 @@
         <v>12.06</v>
       </c>
       <c r="F27" t="n">
-        <v>11.22</v>
+        <v>11.19</v>
       </c>
       <c r="G27" t="n">
         <v>22</v>
@@ -7286,10 +7286,10 @@
         <v>23</v>
       </c>
       <c r="B28" t="n">
-        <v>12.48</v>
+        <v>12.47</v>
       </c>
       <c r="C28" t="n">
-        <v>12.1</v>
+        <v>12.38</v>
       </c>
       <c r="D28" t="n">
         <v>23</v>
@@ -7298,7 +7298,7 @@
         <v>11.73</v>
       </c>
       <c r="F28" t="n">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
       <c r="G28" t="n">
         <v>23</v>
@@ -7313,7 +7313,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>注: 太陽光大/小＝各季節内で日次太陽光発電量（出力制御前）の上位/下位1/3の日（日数: 需要期・夏 62日:62日 / 需要期・冬 91日:91日 / 不需要期 183日:183日）。60分平均価格の時刻別平均。季節定義は月で編集可能（analysis/15）</t>
+          <t>注: 太陽光大/小＝各季節内で日次太陽光発電量（出力制御前）の上位/下位1/3の日（日数: 需要期・夏 92日:92日 / 需要期・冬 91日:90日 / 不需要期 183日:183日）。60分平均価格の時刻別平均。季節定義は月で編集可能（analysis/15）</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>需要期・夏（7-8月）</t>
+          <t>需要期・夏（7-9月）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -7408,10 +7408,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>11.31</v>
+        <v>11.28</v>
       </c>
       <c r="C5" t="n">
-        <v>12.33</v>
+        <v>12.49</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -7420,7 +7420,7 @@
         <v>10.92</v>
       </c>
       <c r="F5" t="n">
-        <v>12.45</v>
+        <v>12.48</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -7437,10 +7437,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>10.5</v>
+        <v>10.63</v>
       </c>
       <c r="C6" t="n">
-        <v>11.34</v>
+        <v>11.57</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -7449,7 +7449,7 @@
         <v>10.73</v>
       </c>
       <c r="F6" t="n">
-        <v>12.27</v>
+        <v>12.3</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -7466,10 +7466,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>10.68</v>
+        <v>10.71</v>
       </c>
       <c r="C7" t="n">
-        <v>11.37</v>
+        <v>11.71</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -7478,7 +7478,7 @@
         <v>10.85</v>
       </c>
       <c r="F7" t="n">
-        <v>12.34</v>
+        <v>12.37</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -7495,10 +7495,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="n">
-        <v>11.04</v>
+        <v>11.13</v>
       </c>
       <c r="C8" t="n">
-        <v>11.84</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -7507,7 +7507,7 @@
         <v>10.91</v>
       </c>
       <c r="F8" t="n">
-        <v>12.5</v>
+        <v>12.53</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -7524,10 +7524,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>11.05</v>
+        <v>11.24</v>
       </c>
       <c r="C9" t="n">
-        <v>12.1</v>
+        <v>12.28</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -7536,7 +7536,7 @@
         <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>12.75</v>
+        <v>12.78</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -7553,10 +7553,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>10.31</v>
+        <v>10.76</v>
       </c>
       <c r="C10" t="n">
-        <v>11.41</v>
+        <v>11.86</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -7565,7 +7565,7 @@
         <v>11.43</v>
       </c>
       <c r="F10" t="n">
-        <v>12.91</v>
+        <v>12.94</v>
       </c>
       <c r="G10" t="n">
         <v>5</v>
@@ -7582,10 +7582,10 @@
         <v>6</v>
       </c>
       <c r="B11" t="n">
-        <v>9.619999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="C11" t="n">
-        <v>10.83</v>
+        <v>11.15</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -7594,7 +7594,7 @@
         <v>12.42</v>
       </c>
       <c r="F11" t="n">
-        <v>14.28</v>
+        <v>14.32</v>
       </c>
       <c r="G11" t="n">
         <v>6</v>
@@ -7611,10 +7611,10 @@
         <v>7</v>
       </c>
       <c r="B12" t="n">
-        <v>8.98</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>10.01</v>
+        <v>10.27</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
@@ -7623,7 +7623,7 @@
         <v>12.53</v>
       </c>
       <c r="F12" t="n">
-        <v>14.25</v>
+        <v>14.29</v>
       </c>
       <c r="G12" t="n">
         <v>7</v>
@@ -7640,10 +7640,10 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="C13" t="n">
-        <v>10.59</v>
+        <v>10.76</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
@@ -7652,7 +7652,7 @@
         <v>11.92</v>
       </c>
       <c r="F13" t="n">
-        <v>13.61</v>
+        <v>13.64</v>
       </c>
       <c r="G13" t="n">
         <v>8</v>
@@ -7669,10 +7669,10 @@
         <v>9</v>
       </c>
       <c r="B14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="C14" t="n">
-        <v>10.41</v>
+        <v>10.75</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
@@ -7681,7 +7681,7 @@
         <v>11.09</v>
       </c>
       <c r="F14" t="n">
-        <v>12.22</v>
+        <v>12.24</v>
       </c>
       <c r="G14" t="n">
         <v>9</v>
@@ -7698,10 +7698,10 @@
         <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>8.6</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>9.369999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -7710,7 +7710,7 @@
         <v>9.539999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10.87</v>
+        <v>10.89</v>
       </c>
       <c r="G15" t="n">
         <v>10</v>
@@ -7727,10 +7727,10 @@
         <v>11</v>
       </c>
       <c r="B16" t="n">
-        <v>8.630000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>9.720000000000001</v>
+        <v>10.05</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -7739,7 +7739,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>11</v>
@@ -7756,10 +7756,10 @@
         <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>8.1</v>
+        <v>7.83</v>
       </c>
       <c r="C17" t="n">
-        <v>8.9</v>
+        <v>9.17</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -7785,10 +7785,10 @@
         <v>13</v>
       </c>
       <c r="B18" t="n">
-        <v>10.37</v>
+        <v>10.01</v>
       </c>
       <c r="C18" t="n">
-        <v>11.46</v>
+        <v>11.8</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -7797,7 +7797,7 @@
         <v>9.279999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>10.49</v>
+        <v>10.5</v>
       </c>
       <c r="G18" t="n">
         <v>13</v>
@@ -7814,10 +7814,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="n">
-        <v>12.05</v>
+        <v>11.89</v>
       </c>
       <c r="C19" t="n">
-        <v>12.68</v>
+        <v>13.19</v>
       </c>
       <c r="D19" t="n">
         <v>14</v>
@@ -7826,7 +7826,7 @@
         <v>10.02</v>
       </c>
       <c r="F19" t="n">
-        <v>11.43</v>
+        <v>11.45</v>
       </c>
       <c r="G19" t="n">
         <v>14</v>
@@ -7843,10 +7843,10 @@
         <v>15</v>
       </c>
       <c r="B20" t="n">
-        <v>13.6</v>
+        <v>14.09</v>
       </c>
       <c r="C20" t="n">
-        <v>15.2</v>
+        <v>15.49</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -7855,7 +7855,7 @@
         <v>11.59</v>
       </c>
       <c r="F20" t="n">
-        <v>13.69</v>
+        <v>13.73</v>
       </c>
       <c r="G20" t="n">
         <v>15</v>
@@ -7872,10 +7872,10 @@
         <v>16</v>
       </c>
       <c r="B21" t="n">
-        <v>16.32</v>
+        <v>17.98</v>
       </c>
       <c r="C21" t="n">
-        <v>17.57</v>
+        <v>18.15</v>
       </c>
       <c r="D21" t="n">
         <v>16</v>
@@ -7884,7 +7884,7 @@
         <v>13.42</v>
       </c>
       <c r="F21" t="n">
-        <v>15.17</v>
+        <v>15.21</v>
       </c>
       <c r="G21" t="n">
         <v>16</v>
@@ -7901,10 +7901,10 @@
         <v>17</v>
       </c>
       <c r="B22" t="n">
-        <v>17.38</v>
+        <v>18.82</v>
       </c>
       <c r="C22" t="n">
-        <v>18.7</v>
+        <v>19.54</v>
       </c>
       <c r="D22" t="n">
         <v>17</v>
@@ -7913,7 +7913,7 @@
         <v>13.98</v>
       </c>
       <c r="F22" t="n">
-        <v>15.82</v>
+        <v>15.87</v>
       </c>
       <c r="G22" t="n">
         <v>17</v>
@@ -7930,10 +7930,10 @@
         <v>18</v>
       </c>
       <c r="B23" t="n">
-        <v>18.49</v>
+        <v>19.04</v>
       </c>
       <c r="C23" t="n">
-        <v>20.51</v>
+        <v>20.74</v>
       </c>
       <c r="D23" t="n">
         <v>18</v>
@@ -7942,7 +7942,7 @@
         <v>13.79</v>
       </c>
       <c r="F23" t="n">
-        <v>15.44</v>
+        <v>15.48</v>
       </c>
       <c r="G23" t="n">
         <v>18</v>
@@ -7959,10 +7959,10 @@
         <v>19</v>
       </c>
       <c r="B24" t="n">
-        <v>18.03</v>
+        <v>17.7</v>
       </c>
       <c r="C24" t="n">
-        <v>19.38</v>
+        <v>19.18</v>
       </c>
       <c r="D24" t="n">
         <v>19</v>
@@ -7971,7 +7971,7 @@
         <v>13.16</v>
       </c>
       <c r="F24" t="n">
-        <v>14.65</v>
+        <v>14.69</v>
       </c>
       <c r="G24" t="n">
         <v>19</v>
@@ -7988,10 +7988,10 @@
         <v>20</v>
       </c>
       <c r="B25" t="n">
-        <v>16.63</v>
+        <v>16.5</v>
       </c>
       <c r="C25" t="n">
-        <v>17.61</v>
+        <v>17.55</v>
       </c>
       <c r="D25" t="n">
         <v>20</v>
@@ -8000,7 +8000,7 @@
         <v>12.99</v>
       </c>
       <c r="F25" t="n">
-        <v>14.05</v>
+        <v>14.09</v>
       </c>
       <c r="G25" t="n">
         <v>20</v>
@@ -8017,10 +8017,10 @@
         <v>21</v>
       </c>
       <c r="B26" t="n">
-        <v>14.4</v>
+        <v>14.41</v>
       </c>
       <c r="C26" t="n">
-        <v>15.62</v>
+        <v>15.32</v>
       </c>
       <c r="D26" t="n">
         <v>21</v>
@@ -8029,7 +8029,7 @@
         <v>12.47</v>
       </c>
       <c r="F26" t="n">
-        <v>13.26</v>
+        <v>13.29</v>
       </c>
       <c r="G26" t="n">
         <v>21</v>
@@ -8046,10 +8046,10 @@
         <v>22</v>
       </c>
       <c r="B27" t="n">
-        <v>12.88</v>
+        <v>12.93</v>
       </c>
       <c r="C27" t="n">
-        <v>14.26</v>
+        <v>14.43</v>
       </c>
       <c r="D27" t="n">
         <v>22</v>
@@ -8058,7 +8058,7 @@
         <v>11.5</v>
       </c>
       <c r="F27" t="n">
-        <v>12.31</v>
+        <v>12.33</v>
       </c>
       <c r="G27" t="n">
         <v>22</v>
@@ -8075,10 +8075,10 @@
         <v>23</v>
       </c>
       <c r="B28" t="n">
-        <v>11.85</v>
+        <v>11.83</v>
       </c>
       <c r="C28" t="n">
-        <v>13.05</v>
+        <v>13.17</v>
       </c>
       <c r="D28" t="n">
         <v>23</v>
@@ -8087,7 +8087,7 @@
         <v>11.42</v>
       </c>
       <c r="F28" t="n">
-        <v>12.13</v>
+        <v>12.15</v>
       </c>
       <c r="G28" t="n">
         <v>23</v>
@@ -8102,7 +8102,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>注: 風力大/小＝各季節内で日次風力発電量（制御前）の上位/下位1/3の日（日数: 需要期・夏 62:62 / 需要期・冬 91:91 / 不需要期 183:183）</t>
+          <t>注: 風力大/小＝各季節内で日次風力発電量（制御前）の上位/下位1/3の日（日数: 需要期・夏 92:92 / 需要期・冬 91:90 / 不需要期 183:183）</t>
         </is>
       </c>
     </row>
@@ -8200,16 +8200,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.72</v>
+        <v>10.89</v>
       </c>
       <c r="D4" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="F4" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -8220,10 +8220,10 @@
         <v>32.1</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="K4" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="5">
@@ -8238,16 +8238,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10.4</v>
+        <v>10.81</v>
       </c>
       <c r="D5" t="n">
-        <v>30.4</v>
+        <v>31.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -8258,10 +8258,10 @@
         <v>31.7</v>
       </c>
       <c r="J5" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>30.4</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="6">
@@ -8276,16 +8276,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10.38</v>
+        <v>11.3</v>
       </c>
       <c r="D6" t="n">
-        <v>30.7</v>
+        <v>33.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06</v>
+        <v>0.35</v>
       </c>
       <c r="F6" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>15.3</v>
       </c>
       <c r="K6" t="n">
-        <v>30.7</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="7">
@@ -8314,10 +8314,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.24</v>
+        <v>7.3</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="E7" t="n">
         <v>0.02</v>
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.43</v>
+        <v>6.38</v>
       </c>
       <c r="D8" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -8700,13 +8700,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>12.75</v>
+        <v>12.93</v>
       </c>
       <c r="D5" t="n">
-        <v>10.3</v>
+        <v>10.32</v>
       </c>
       <c r="E5" t="n">
         <v>3.82</v>
@@ -8743,16 +8743,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="C6" t="n">
-        <v>13.6</v>
+        <v>13.83</v>
       </c>
       <c r="D6" t="n">
-        <v>11.6</v>
+        <v>11.25</v>
       </c>
       <c r="E6" t="n">
-        <v>4.24</v>
+        <v>4.08</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
@@ -8786,16 +8786,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="C7" t="n">
-        <v>12.41</v>
+        <v>12.79</v>
       </c>
       <c r="D7" t="n">
-        <v>10.37</v>
+        <v>11.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3.71</v>
+        <v>4.15</v>
       </c>
       <c r="F7" t="n">
         <v>9.9</v>
@@ -8832,13 +8832,13 @@
         <v>7.1</v>
       </c>
       <c r="C8" t="n">
-        <v>12.08</v>
+        <v>12.71</v>
       </c>
       <c r="D8" t="n">
-        <v>10.02</v>
+        <v>10.29</v>
       </c>
       <c r="E8" t="n">
-        <v>3.57</v>
+        <v>3.72</v>
       </c>
       <c r="F8" t="n">
         <v>13.4</v>
@@ -8872,16 +8872,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="C9" t="n">
-        <v>12.22</v>
+        <v>12.01</v>
       </c>
       <c r="D9" t="n">
-        <v>10.23</v>
+        <v>11.67</v>
       </c>
       <c r="E9" t="n">
-        <v>3.67</v>
+        <v>4.2</v>
       </c>
       <c r="F9" t="n">
         <v>17.7</v>
@@ -8989,16 +8989,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="C14" t="n">
-        <v>13.09</v>
+        <v>13.65</v>
       </c>
       <c r="D14" t="n">
-        <v>9.050000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="E14" t="n">
-        <v>3.36</v>
+        <v>3.59</v>
       </c>
       <c r="F14" t="n">
         <v>2.6</v>
@@ -9032,16 +9032,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="C15" t="n">
-        <v>13.15</v>
+        <v>13.48</v>
       </c>
       <c r="D15" t="n">
-        <v>10.93</v>
+        <v>10.95</v>
       </c>
       <c r="E15" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="F15" t="n">
         <v>4.6</v>
@@ -9075,16 +9075,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="C16" t="n">
-        <v>12.45</v>
+        <v>12.57</v>
       </c>
       <c r="D16" t="n">
-        <v>10.15</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="F16" t="n">
         <v>5.6</v>
@@ -9121,13 +9121,13 @@
         <v>12.2</v>
       </c>
       <c r="C17" t="n">
-        <v>12.03</v>
+        <v>12.39</v>
       </c>
       <c r="D17" t="n">
-        <v>9.9</v>
+        <v>12.04</v>
       </c>
       <c r="E17" t="n">
-        <v>3.59</v>
+        <v>4.35</v>
       </c>
       <c r="F17" t="n">
         <v>6.6</v>
@@ -9161,16 +9161,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="C18" t="n">
-        <v>12.33</v>
+        <v>12.17</v>
       </c>
       <c r="D18" t="n">
-        <v>12.57</v>
+        <v>12.6</v>
       </c>
       <c r="E18" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="F18" t="n">
         <v>8.800000000000001</v>
@@ -13057,19 +13057,19 @@
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003</v>
+        <v>0.126</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.02</v>
+        <v>-0.019</v>
       </c>
       <c r="P4" t="n">
-        <v>0.175</v>
+        <v>0.191</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.137</v>
+        <v>0.141</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -13113,19 +13113,19 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.036</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005</v>
+        <v>0.203</v>
       </c>
       <c r="O5" t="n">
         <v>-0.018</v>
       </c>
       <c r="P5" t="n">
-        <v>0.233</v>
+        <v>0.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.139</v>
+        <v>0.142</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -13169,19 +13169,19 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007</v>
+        <v>0.315</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.018</v>
+        <v>-0.017</v>
       </c>
       <c r="P6" t="n">
-        <v>0.266</v>
+        <v>0.283</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.143</v>
+        <v>0.146</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -13225,19 +13225,19 @@
         <v>0.9999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.082</v>
+        <v>-0.022</v>
       </c>
       <c r="N7" t="n">
-        <v>0.013</v>
+        <v>0.483</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.007</v>
+        <v>-0.006</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.717</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.149</v>
+        <v>0.152</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -13281,19 +13281,19 @@
         <v>0.9998</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="N8" t="n">
-        <v>0.037</v>
+        <v>0.836</v>
       </c>
       <c r="O8" t="n">
         <v>0.006</v>
       </c>
       <c r="P8" t="n">
-        <v>0.753</v>
+        <v>0.726</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.158</v>
+        <v>0.161</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -13506,13 +13506,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.4598</v>
+        <v>-0.4056</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3188</v>
+        <v>-0.2677</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -13535,13 +13535,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.2819</v>
+        <v>-0.2455</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2193</v>
+        <v>-0.206</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -13564,16 +13564,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.7557</v>
+        <v>-0.7607</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6403</v>
+        <v>-0.6442</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0024</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="7">
@@ -13593,13 +13593,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.3538</v>
+        <v>-0.3529</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3024</v>
+        <v>-0.3018</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -13622,13 +13622,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.347</v>
+        <v>-0.3512</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1929</v>
+        <v>-0.1965</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -13651,13 +13651,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.3578</v>
+        <v>-0.3547</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2954</v>
+        <v>-0.2931</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -13680,16 +13680,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.0453</v>
+        <v>0.0013</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3188</v>
+        <v>0.9721</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0034</v>
+        <v>0.0299</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9361</v>
+        <v>0.3964</v>
       </c>
     </row>
     <row r="11">
@@ -13709,16 +13709,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1285</v>
+        <v>-0.0574</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0018</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0779</v>
+        <v>-0.0259</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0444</v>
+        <v>0.4436</v>
       </c>
     </row>
     <row r="12">
@@ -13738,16 +13738,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3071</v>
+        <v>-0.3082</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0039</v>
+        <v>0.0038</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.225</v>
+        <v>-0.2263</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0613</v>
       </c>
     </row>
     <row r="13">
@@ -13767,13 +13767,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1308</v>
+        <v>-0.1305</v>
       </c>
       <c r="E13" t="n">
         <v>0.0002</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1402</v>
+        <v>-0.1399</v>
       </c>
       <c r="G13" t="n">
         <v>0.0002</v>
@@ -13796,13 +13796,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.0935</v>
+        <v>0.0926</v>
       </c>
       <c r="E14" t="n">
         <v>0.0001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1179</v>
+        <v>0.1166</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -13825,16 +13825,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.0276</v>
+        <v>-0.0268</v>
       </c>
       <c r="E15" t="n">
-        <v>0.203</v>
+        <v>0.2155</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0086</v>
+        <v>-0.0076</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6712</v>
+        <v>0.7069</v>
       </c>
     </row>
     <row r="16">
@@ -13854,16 +13854,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.0961</v>
+        <v>0.033</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4354</v>
+        <v>0.7468</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0065</v>
+        <v>0.1013</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9542</v>
+        <v>0.2813</v>
       </c>
     </row>
     <row r="17">
@@ -13883,16 +13883,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.3485</v>
+        <v>-0.1564</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0025</v>
+        <v>0.1185</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1852</v>
+        <v>-0.0533</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0868</v>
+        <v>0.5648</v>
       </c>
     </row>
     <row r="18">
@@ -13912,16 +13912,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.8034</v>
+        <v>-0.8066</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0056</v>
+        <v>0.0054</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5616</v>
+        <v>-0.5649</v>
       </c>
       <c r="G18" t="n">
-        <v>0.089</v>
+        <v>0.0872</v>
       </c>
     </row>
     <row r="19">
@@ -13941,13 +13941,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.3639</v>
+        <v>-0.3631</v>
       </c>
       <c r="E19" t="n">
         <v>0.0002</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3887</v>
+        <v>-0.3878</v>
       </c>
       <c r="G19" t="n">
         <v>0.0002</v>
@@ -13970,13 +13970,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.2352</v>
+        <v>0.2326</v>
       </c>
       <c r="E20" t="n">
         <v>0.0002</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3168</v>
+        <v>0.3138</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -13999,16 +13999,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0668</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2281</v>
+        <v>0.2431</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0176</v>
+        <v>-0.015</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7418</v>
+        <v>0.778</v>
       </c>
     </row>
     <row r="22">
@@ -14028,16 +14028,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.0639</v>
+        <v>-0.0649</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0383</v>
+        <v>-0.0394</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0008</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="23">
@@ -14057,16 +14057,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.0408</v>
+        <v>-0.0132</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6875</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1477</v>
+        <v>0.1352</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1917</v>
+        <v>0.1251</v>
       </c>
     </row>
     <row r="24">
@@ -14086,16 +14086,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.0614</v>
+        <v>-0.062</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0025</v>
+        <v>0.0023</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0555</v>
+        <v>-0.0564</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0267</v>
+        <v>0.0245</v>
       </c>
     </row>
     <row r="25">
@@ -14115,16 +14115,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.2726</v>
+        <v>-0.2721</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1703</v>
+        <v>0.1713</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3245</v>
+        <v>-0.3255</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1879</v>
+        <v>0.1868</v>
       </c>
     </row>
     <row r="26">
@@ -14144,13 +14144,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.0549</v>
+        <v>-0.0555</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0467</v>
+        <v>-0.0475</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -14173,16 +14173,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0655</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3016</v>
+        <v>0.3264</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0112</v>
+        <v>0.006</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8516</v>
+        <v>0.9198</v>
       </c>
     </row>
     <row r="28">
@@ -14202,16 +14202,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.0059</v>
+        <v>0.0095</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3851</v>
+        <v>0.0935</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0017</v>
+        <v>0.0016</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7924</v>
+        <v>0.7733</v>
       </c>
     </row>
     <row r="29">
@@ -14231,16 +14231,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.0431</v>
       </c>
       <c r="E29" t="n">
-        <v>0.229</v>
+        <v>0.5629</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1022</v>
+        <v>-0.0477</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2585</v>
+        <v>0.5405</v>
       </c>
     </row>
     <row r="30">
@@ -14269,7 +14269,7 @@
         <v>0.0308</v>
       </c>
       <c r="G30" t="n">
-        <v>0.032</v>
+        <v>0.0321</v>
       </c>
     </row>
     <row r="31">
@@ -14289,16 +14289,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-0.1357</v>
+        <v>-0.1349</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2022</v>
+        <v>0.2052</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2345</v>
+        <v>-0.2342</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="32">
@@ -14324,7 +14324,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0363</v>
+        <v>0.0362</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -14347,16 +14347,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1148</v>
+        <v>0.115</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0064</v>
+        <v>0.0062</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0789</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0243</v>
+        <v>0.0247</v>
       </c>
     </row>
     <row r="34">
@@ -14376,16 +14376,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.0162</v>
+        <v>0.0271</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3651</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0012</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9449</v>
+        <v>0.5272</v>
       </c>
     </row>
     <row r="35">
@@ -14405,16 +14405,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-0.2479</v>
+        <v>0.1261</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2632</v>
+        <v>0.5276</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2683</v>
+        <v>-0.1202</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2572</v>
+        <v>0.5606</v>
       </c>
     </row>
     <row r="36">
@@ -14434,16 +14434,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.1229</v>
+        <v>0.1228</v>
       </c>
       <c r="E36" t="n">
         <v>0.0001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0878</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0205</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="37">
@@ -14463,16 +14463,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-0.3509</v>
+        <v>-0.3485</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2067</v>
+        <v>0.2098</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6181</v>
+        <v>-0.6176</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0648</v>
+        <v>0.06510000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -14492,13 +14492,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.1041</v>
+        <v>0.1039</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0862</v>
+        <v>0.0859</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -14521,16 +14521,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.2751</v>
+        <v>0.2748</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0163</v>
+        <v>0.0162</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1751</v>
+        <v>0.1736</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0608</v>
+        <v>0.06270000000000001</v>
       </c>
     </row>
   </sheetData>
